--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,30 +487,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>需求权重</t>
+          <t>立绘差分</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>需求数下限</t>
+          <t>序列帧</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>需求数上限</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>立绘差分</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>序列帧</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>对话池</t>
         </is>
@@ -549,30 +534,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>needTagWeights</t>
+          <t>portraits</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>needCountMin</t>
+          <t>sheetPath</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>needCountMax</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>portraits</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>sheetPath</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>dialoguePool</t>
         </is>
@@ -603,26 +573,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>木料*5*必/天然*3/精加工*2</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
           <t>平静=OutGameUI/Guests/fox</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/orange_cat</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Pool_fox</t>
         </is>
@@ -653,26 +612,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>材料*4*必/精加工*4/能源*2</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
           <t>平静=OutGameUI/Guests/crow</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/rottweiler</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Pool_crow</t>
         </is>
@@ -703,26 +651,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>能源*4*必/精加工*3</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
           <t>平静=OutGameUI/Guests/hedgehog</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/wangcai</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Pool_hedgehog</t>
         </is>
@@ -753,26 +690,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>天然*5*必/木料*3</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
           <t>平静=OutGameUI/Guests/rabbit</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/xueqiu</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Pool_rabbit</t>
         </is>

--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -495,11 +495,6 @@
           <t>序列帧</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>对话池</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -542,11 +537,6 @@
           <t>sheetPath</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>dialoguePool</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -581,11 +571,6 @@
           <t>OutGameUI/Visitors/orange_cat</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Pool_fox</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -620,11 +605,6 @@
           <t>OutGameUI/Visitors/rottweiler</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Pool_crow</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -659,11 +639,6 @@
           <t>OutGameUI/Visitors/wangcai</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Pool_hedgehog</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -696,11 +671,6 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/xueqiu</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Pool_rabbit</t>
         </is>
       </c>
     </row>

--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -482,15 +482,10 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>跨天留宿概率%</t>
+          <t>默认立绘ID</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>立绘差分</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>序列帧</t>
         </is>
@@ -524,15 +519,10 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>stayOvernightPercent</t>
+          <t>defaultPortraitId</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>portraits</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>sheetPath</t>
         </is>
@@ -558,15 +548,12 @@
       <c r="E3" t="n">
         <v>3600</v>
       </c>
-      <c r="F3" t="n">
-        <v>30</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fox_平静</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>平静=OutGameUI/Guests/fox</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/orange_cat</t>
         </is>
@@ -592,15 +579,12 @@
       <c r="E4" t="n">
         <v>2400</v>
       </c>
-      <c r="F4" t="n">
-        <v>10</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>crow_平静</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>平静=OutGameUI/Guests/crow</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/rottweiler</t>
         </is>
@@ -626,15 +610,12 @@
       <c r="E5" t="n">
         <v>3000</v>
       </c>
-      <c r="F5" t="n">
-        <v>20</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hedgehog_平静</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>平静=OutGameUI/Guests/hedgehog</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/wangcai</t>
         </is>
@@ -660,15 +641,12 @@
       <c r="E6" t="n">
         <v>6000</v>
       </c>
-      <c r="F6" t="n">
-        <v>60</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rabbit_平静</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>平静=OutGameUI/Guests/rabbit</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>OutGameUI/Visitors/xueqiu</t>
         </is>

--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -1,54 +1,217 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\2026MasterHouse\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541E556B-01EA-4D99-B444-AC84C598E460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="5295" yWindow="2475" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="种族" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="种族" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+  <si>
+    <t>种族id</t>
+  </si>
+  <si>
+    <t>显示名</t>
+  </si>
+  <si>
+    <t>等搭话超时tick</t>
+  </si>
+  <si>
+    <t>等交货超时tick</t>
+  </si>
+  <si>
+    <t>闲逛上限tick</t>
+  </si>
+  <si>
+    <t>默认立绘ID</t>
+  </si>
+  <si>
+    <t>序列帧</t>
+  </si>
+  <si>
+    <t>raceId</t>
+  </si>
+  <si>
+    <t>displayName</t>
+  </si>
+  <si>
+    <t>waitTalkTimeoutTicks</t>
+  </si>
+  <si>
+    <t>waitDeliverTimeoutTicks</t>
+  </si>
+  <si>
+    <t>wanderMaxTicks</t>
+  </si>
+  <si>
+    <t>defaultPortraitId</t>
+  </si>
+  <si>
+    <t>sheetPath</t>
+  </si>
+  <si>
+    <t>兔族</t>
+  </si>
+  <si>
+    <t>rabbit_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Visitors/rabbit</t>
+  </si>
+  <si>
+    <t>goat</t>
+  </si>
+  <si>
+    <t>羊族</t>
+  </si>
+  <si>
+    <t>goat_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Visitors/goat</t>
+  </si>
+  <si>
+    <t>wolf</t>
+  </si>
+  <si>
+    <t>狼族</t>
+  </si>
+  <si>
+    <t>wolf_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Visitors/wolf</t>
+  </si>
+  <si>
+    <t>leopard</t>
+  </si>
+  <si>
+    <t>豹族</t>
+  </si>
+  <si>
+    <t>leopard_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Visitors/leopard</t>
+  </si>
+  <si>
+    <t>cheetah</t>
+  </si>
+  <si>
+    <t>猎豹族</t>
+  </si>
+  <si>
+    <t>cheetah_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Visitors/cheetah</t>
+  </si>
+  <si>
+    <t>ox</t>
+  </si>
+  <si>
+    <t>牛族</t>
+  </si>
+  <si>
+    <t>ox_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Visitors/ox</t>
+  </si>
+  <si>
+    <t>cat</t>
+  </si>
+  <si>
+    <t>猫族</t>
+  </si>
+  <si>
+    <t>cat_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Visitors/cat</t>
+  </si>
+  <si>
+    <t>yak</t>
+  </si>
+  <si>
+    <t>牦牛族</t>
+  </si>
+  <si>
+    <t>yak_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Visitors/yak</t>
+  </si>
+  <si>
+    <t>rabbit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
+        <fgColor rgb="FF4F81BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
+        <fgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,86 +228,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -432,227 +536,254 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>种族id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>显示名</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>等搭话超时tick</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>等交货超时tick</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>闲逛上限tick</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>默认立绘ID</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>序列帧</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>raceId</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>displayName</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>waitTalkTimeoutTicks</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>waitDeliverTimeoutTicks</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>wanderMaxTicks</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>defaultPortraitId</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>sheetPath</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>fox</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>狐族</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>4200</v>
+      </c>
+      <c r="D3">
+        <v>7200</v>
+      </c>
+      <c r="E3">
+        <v>6000</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>3600</v>
+      </c>
+      <c r="D4">
+        <v>6600</v>
+      </c>
+      <c r="E4">
+        <v>5400</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5">
+        <v>1800</v>
+      </c>
+      <c r="D5">
+        <v>3600</v>
+      </c>
+      <c r="E5">
+        <v>2400</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>2400</v>
+      </c>
+      <c r="D6">
+        <v>4800</v>
+      </c>
+      <c r="E6">
         <v>3000</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7">
+        <v>2100</v>
+      </c>
+      <c r="D7">
+        <v>4200</v>
+      </c>
+      <c r="E7">
+        <v>2700</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>4800</v>
+      </c>
+      <c r="D8">
+        <v>8400</v>
+      </c>
+      <c r="E8">
+        <v>6600</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9">
+        <v>3000</v>
+      </c>
+      <c r="D9">
         <v>6000</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E9">
         <v>3600</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>fox_平静</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Visitors/orange_cat</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>crow</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>鸦族</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3600</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>crow_平静</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>OutGameUI/Visitors/rottweiler</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>hedgehog</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>猬族</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2400</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4800</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>hedgehog_平静</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>OutGameUI/Visitors/wangcai</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>rabbit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>兔族</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>4200</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7200</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>rabbit_平静</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>OutGameUI/Visitors/xueqiu</t>
-        </is>
+      <c r="F9" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10">
+        <v>3900</v>
+      </c>
+      <c r="D10">
+        <v>7000</v>
+      </c>
+      <c r="E10">
+        <v>5600</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\2026MasterHouse\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541E556B-01EA-4D99-B444-AC84C598E460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077AECA9-9ADC-40FA-9808-918A54EF9D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5295" yWindow="2475" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="种族" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>sheetPath</t>
   </si>
   <si>
-    <t>兔族</t>
-  </si>
-  <si>
     <t>rabbit_平静</t>
   </si>
   <si>
@@ -76,9 +73,6 @@
     <t>goat</t>
   </si>
   <si>
-    <t>羊族</t>
-  </si>
-  <si>
     <t>goat_平静</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>wolf</t>
   </si>
   <si>
-    <t>狼族</t>
-  </si>
-  <si>
     <t>wolf_平静</t>
   </si>
   <si>
@@ -100,9 +91,6 @@
     <t>leopard</t>
   </si>
   <si>
-    <t>豹族</t>
-  </si>
-  <si>
     <t>leopard_平静</t>
   </si>
   <si>
@@ -112,9 +100,6 @@
     <t>cheetah</t>
   </si>
   <si>
-    <t>猎豹族</t>
-  </si>
-  <si>
     <t>cheetah_平静</t>
   </si>
   <si>
@@ -124,9 +109,6 @@
     <t>ox</t>
   </si>
   <si>
-    <t>牛族</t>
-  </si>
-  <si>
     <t>ox_平静</t>
   </si>
   <si>
@@ -136,9 +118,6 @@
     <t>cat</t>
   </si>
   <si>
-    <t>猫族</t>
-  </si>
-  <si>
     <t>cat_平静</t>
   </si>
   <si>
@@ -148,9 +127,6 @@
     <t>yak</t>
   </si>
   <si>
-    <t>牦牛族</t>
-  </si>
-  <si>
     <t>yak_平静</t>
   </si>
   <si>
@@ -158,6 +134,38 @@
   </si>
   <si>
     <t>rabbit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘻洋羊</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑喵警长</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹冲冲</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>豹酷酷</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉嚎</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛小顿</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>兔米露</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛莱老师</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -600,10 +608,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C3">
         <v>4200</v>
@@ -615,18 +623,18 @@
         <v>6000</v>
       </c>
       <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>3600</v>
@@ -638,18 +646,18 @@
         <v>5400</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>1800</v>
@@ -661,18 +669,18 @@
         <v>2400</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>2400</v>
@@ -684,18 +692,18 @@
         <v>3000</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>2100</v>
@@ -707,18 +715,18 @@
         <v>2700</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>4800</v>
@@ -730,18 +738,18 @@
         <v>6600</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>3000</v>
@@ -753,18 +761,18 @@
         <v>3600</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>3900</v>
@@ -776,14 +784,15 @@
         <v>5600</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077AECA9-9ADC-40FA-9808-918A54EF9D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63ED0AAF-F09E-4A00-9FF9-05CF3F4B56D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -677,7 +677,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
         <v>41</v>
@@ -692,7 +692,7 @@
         <v>3000</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -700,7 +700,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>40</v>
@@ -715,7 +715,7 @@
         <v>2700</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
         <v>27</v>

--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65CA07D-57F7-47B8-8BAF-5A33CD947269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A3A148-623E-4667-98EA-47E8F8E8B5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1004,7 +1004,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>46</v>
@@ -1045,7 +1045,7 @@
         <v>55</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>56</v>

--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A3A148-623E-4667-98EA-47E8F8E8B5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD6781C-88A9-4F9A-8849-155AD7B6B637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="种族" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
   <si>
     <t>种族id</t>
   </si>
@@ -229,34 +229,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>豹冲冲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑猫警官</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>豹酷酷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘉嚎</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛小顿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OutGameUI/Visitors/yak</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>兔米露</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>称号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -329,10 +305,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>牛莱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>收集亮晶晶发卡、研究饭撒姿势、读粉丝寄来的手写信</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -358,6 +330,38 @@
   </si>
   <si>
     <t>咖啡、办公、欣赏自己的帅气侧脸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地下偶像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>民宿老板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集团总裁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>棒球队-队长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>棒球队-球员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>私家侦探</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>警长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢琴老师</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -805,7 +809,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -887,19 +891,19 @@
         <v>49</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="J3" s="3">
         <v>4</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="49.5">
@@ -928,19 +932,19 @@
         <v>51</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J4" s="3">
         <v>3</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="49.5">
@@ -969,19 +973,19 @@
         <v>54</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="J5" s="3">
         <v>4</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="82.5">
@@ -1010,19 +1014,19 @@
         <v>46</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="J6" s="3">
         <v>3</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="99">
@@ -1051,19 +1055,19 @@
         <v>56</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="J7" s="3">
         <v>3</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="49.5">
@@ -1092,19 +1096,19 @@
         <v>58</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="J8" s="3">
         <v>4</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="115.5">
@@ -1133,19 +1137,19 @@
         <v>60</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="J9" s="3">
         <v>3</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="66">
@@ -1168,25 +1172,25 @@
         <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>62</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J10" s="3">
         <v>3</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/访客种族表.xlsx
+++ b/Excel/访客种族表.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD6781C-88A9-4F9A-8849-155AD7B6B637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55885B7-7BCE-4C41-91B7-12F0F327D5B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47145" yWindow="3540" windowWidth="19635" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="种族" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -369,7 +380,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -767,7 +778,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
     <col min="2" max="2" width="10" style="3" customWidth="1"/>
@@ -783,7 +794,7 @@
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -824,7 +835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -865,7 +876,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="49.5">
+    <row r="3" spans="1:13" ht="49.5" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>25</v>
       </c>
@@ -873,13 +884,13 @@
         <v>26</v>
       </c>
       <c r="C3" s="3">
-        <v>4200</v>
+        <v>840</v>
       </c>
       <c r="D3" s="3">
-        <v>7200</v>
+        <v>1440</v>
       </c>
       <c r="E3" s="3">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>48</v>
@@ -906,7 +917,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="49.5">
+    <row r="4" spans="1:13" ht="49.5" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
@@ -914,13 +925,13 @@
         <v>29</v>
       </c>
       <c r="C4" s="3">
-        <v>3600</v>
+        <v>720</v>
       </c>
       <c r="D4" s="3">
-        <v>6600</v>
+        <v>1320</v>
       </c>
       <c r="E4" s="3">
-        <v>5400</v>
+        <v>1080</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>50</v>
@@ -947,7 +958,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="49.5">
+    <row r="5" spans="1:13" ht="49.5" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -955,13 +966,13 @@
         <v>32</v>
       </c>
       <c r="C5" s="3">
-        <v>1800</v>
+        <v>360</v>
       </c>
       <c r="D5" s="3">
-        <v>3600</v>
+        <v>720</v>
       </c>
       <c r="E5" s="3">
-        <v>2400</v>
+        <v>480</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>52</v>
@@ -988,7 +999,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="82.5">
+    <row r="6" spans="1:13" ht="82.5" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
@@ -996,13 +1007,13 @@
         <v>34</v>
       </c>
       <c r="C6" s="3">
-        <v>2400</v>
+        <v>480</v>
       </c>
       <c r="D6" s="3">
-        <v>4800</v>
+        <v>960</v>
       </c>
       <c r="E6" s="3">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>53</v>
@@ -1029,7 +1040,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="99">
+    <row r="7" spans="1:13" ht="99" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>35</v>
       </c>
@@ -1037,13 +1048,13 @@
         <v>36</v>
       </c>
       <c r="C7" s="3">
-        <v>2100</v>
+        <v>420</v>
       </c>
       <c r="D7" s="3">
-        <v>4200</v>
+        <v>840</v>
       </c>
       <c r="E7" s="3">
-        <v>2700</v>
+        <v>540</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>55</v>
@@ -1070,7 +1081,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="49.5">
+    <row r="8" spans="1:13" ht="49.5" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>37</v>
       </c>
@@ -1078,13 +1089,13 @@
         <v>38</v>
       </c>
       <c r="C8" s="3">
-        <v>4800</v>
+        <v>960</v>
       </c>
       <c r="D8" s="3">
-        <v>8400</v>
+        <v>1680</v>
       </c>
       <c r="E8" s="3">
-        <v>6600</v>
+        <v>1320</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>57</v>
@@ -1111,7 +1122,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="115.5">
+    <row r="9" spans="1:13" ht="115.5" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>40</v>
       </c>
@@ -1119,13 +1130,13 @@
         <v>41</v>
       </c>
       <c r="C9" s="3">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="D9" s="3">
-        <v>6000</v>
+        <v>1200</v>
       </c>
       <c r="E9" s="3">
-        <v>3600</v>
+        <v>720</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>59</v>
@@ -1152,7 +1163,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="66">
+    <row r="10" spans="1:13" ht="66" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>43</v>
       </c>
@@ -1160,13 +1171,13 @@
         <v>44</v>
       </c>
       <c r="C10" s="3">
-        <v>3900</v>
+        <v>780</v>
       </c>
       <c r="D10" s="3">
-        <v>7000</v>
+        <v>1400</v>
       </c>
       <c r="E10" s="3">
-        <v>5600</v>
+        <v>1120</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>61</v>
